--- a/StructureDefinition-openimis-payment-notice.xlsx
+++ b/StructureDefinition-openimis-payment-notice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5276,7 +5276,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>22</v>
@@ -5857,7 +5857,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-payment-notice.xlsx
+++ b/StructureDefinition-openimis-payment-notice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-payment-notice.xlsx
+++ b/StructureDefinition-openimis-payment-notice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
